--- a/data/taxonomic_counts/GS-Liu2021-B_taxonomic_counts.xlsx
+++ b/data/taxonomic_counts/GS-Liu2021-B_taxonomic_counts.xlsx
@@ -1,117 +1,144 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_rechecked_precise_red/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Asgard_Eukaryote_Data/data/taxonomic_counts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115AF564-1817-BB4B-9A2F-6568660F678E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63516D22-4555-0B4D-84A3-37014073C130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Caption" sheetId="10" r:id="rId1"/>
-    <sheet name="Archaea_Phylum" sheetId="1" r:id="rId2"/>
-    <sheet name="Archaea_Class" sheetId="2" r:id="rId3"/>
-    <sheet name="Archaea_Order" sheetId="3" r:id="rId4"/>
-    <sheet name="Bacteria_Phylum" sheetId="4" r:id="rId5"/>
-    <sheet name="Bacteria_Class" sheetId="5" r:id="rId6"/>
-    <sheet name="Bacteria_Order" sheetId="6" r:id="rId7"/>
-    <sheet name="Eukaryota_Phylum" sheetId="7" r:id="rId8"/>
-    <sheet name="Eukaryota_Class" sheetId="8" r:id="rId9"/>
-    <sheet name="Eukaryota_Order" sheetId="9" r:id="rId10"/>
+    <sheet name="Caption" sheetId="1" r:id="rId1"/>
+    <sheet name="Archaea_Phylum" sheetId="2" r:id="rId2"/>
+    <sheet name="Archaea_Class" sheetId="3" r:id="rId3"/>
+    <sheet name="Archaea_Order" sheetId="4" r:id="rId4"/>
+    <sheet name="Bacteria_Phylum" sheetId="5" r:id="rId5"/>
+    <sheet name="Bacteria_Class" sheetId="6" r:id="rId6"/>
+    <sheet name="Bacteria_Order" sheetId="7" r:id="rId7"/>
+    <sheet name="Eukaryota_Phylum" sheetId="8" r:id="rId8"/>
+    <sheet name="Eukaryota_Class" sheetId="9" r:id="rId9"/>
+    <sheet name="Eukaryota_Order" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="431">
+  <si>
+    <t>Supplementary Table 20 | Final taxonomic counts of retained genomes in GS-Liu2021-B at the phylum, class and order levels.</t>
+  </si>
+  <si>
+    <t>Description:</t>
+  </si>
+  <si>
+    <t>This Excel file contains the final taxonomic counts of genomes retained in the GS-Liu2021-B dataset after hierarchical taxonomic balancing.</t>
+  </si>
+  <si>
+    <t>The file includes the following sheets:</t>
+  </si>
+  <si>
+    <t>Archaea_Phylum</t>
+  </si>
+  <si>
+    <t>Archaea_Class</t>
+  </si>
+  <si>
+    <t>Archaea_Order</t>
+  </si>
+  <si>
+    <t>Bacteria_Phylum</t>
+  </si>
+  <si>
+    <t>Bacteria_Class</t>
+  </si>
+  <si>
+    <t>Bacteria_Order</t>
+  </si>
+  <si>
+    <t>Eukaryota_Phylum</t>
+  </si>
+  <si>
+    <t>Eukaryota_Class</t>
+  </si>
+  <si>
+    <t>Eukaryota_Order</t>
+  </si>
+  <si>
+    <t>Each sheet lists the corresponding taxa and the number of genomes retained (N_genomes) at the indicated taxonomic rank for GS-Liu2021-B.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Phylum</t>
+  </si>
+  <si>
+    <t>N_genomes</t>
+  </si>
+  <si>
+    <t>Asgard</t>
+  </si>
+  <si>
+    <t>Asgardarchaeota</t>
+  </si>
+  <si>
+    <t>TACK</t>
+  </si>
+  <si>
+    <t>Korarchaeota</t>
+  </si>
+  <si>
+    <t>Thermoproteota</t>
+  </si>
+  <si>
+    <t>Euryarchaeota</t>
+  </si>
+  <si>
+    <t>Altiarchaeota</t>
+  </si>
+  <si>
+    <t>Hadarchaeota</t>
+  </si>
+  <si>
+    <t>Halobacteriota</t>
+  </si>
+  <si>
+    <t>Methanobacteriota</t>
+  </si>
+  <si>
+    <t>Methanobacteriota_B</t>
+  </si>
+  <si>
+    <t>Nanohalarchaeota</t>
+  </si>
+  <si>
+    <t>Thermoplasmatota</t>
+  </si>
+  <si>
+    <t>DPANN</t>
+  </si>
   <si>
     <t>Aenigmatarchaeota</t>
   </si>
   <si>
-    <t>Altiarchaeota</t>
-  </si>
-  <si>
-    <t>Asgardarchaeota</t>
-  </si>
-  <si>
-    <t>Hadarchaeota</t>
-  </si>
-  <si>
-    <t>Halobacteriota</t>
-  </si>
-  <si>
     <t>Iainarchaeota</t>
   </si>
   <si>
-    <t>Korarchaeota</t>
-  </si>
-  <si>
-    <t>Methanobacteriota</t>
-  </si>
-  <si>
-    <t>Methanobacteriota_B</t>
-  </si>
-  <si>
     <t>Micrarchaeota</t>
   </si>
   <si>
     <t>Nanobdellota</t>
   </si>
   <si>
-    <t>Nanohalarchaeota</t>
-  </si>
-  <si>
-    <t>Thermoplasmatota</t>
-  </si>
-  <si>
-    <t>Thermoproteota</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Phylum</t>
-  </si>
-  <si>
-    <t>N_genomes</t>
-  </si>
-  <si>
-    <t>DPANN</t>
-  </si>
-  <si>
-    <t>Euryarchaeota</t>
-  </si>
-  <si>
-    <t>Asgard</t>
-  </si>
-  <si>
-    <t>TACK</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Phylum</t>
-  </si>
-  <si>
     <t>Class</t>
   </si>
   <si>
-    <t>N_genomes</t>
-  </si>
-  <si>
-    <t>Asgard</t>
-  </si>
-  <si>
-    <t>Asgardarchaeota</t>
-  </si>
-  <si>
     <t>Asgardarchaeia</t>
   </si>
   <si>
@@ -148,21 +175,12 @@
     <t>Wukongarchaeia</t>
   </si>
   <si>
-    <t>TACK</t>
-  </si>
-  <si>
-    <t>Korarchaeota</t>
-  </si>
-  <si>
     <t>JAOZGF01</t>
   </si>
   <si>
     <t>Korarchaeia</t>
   </si>
   <si>
-    <t>Thermoproteota</t>
-  </si>
-  <si>
     <t>Bathyarchaeia</t>
   </si>
   <si>
@@ -190,24 +208,12 @@
     <t>Thermoprotei_A</t>
   </si>
   <si>
-    <t>Euryarchaeota</t>
-  </si>
-  <si>
-    <t>Altiarchaeota</t>
-  </si>
-  <si>
     <t>Altiarchaeia</t>
   </si>
   <si>
-    <t>Hadarchaeota</t>
-  </si>
-  <si>
     <t>Hadarchaeia</t>
   </si>
   <si>
-    <t>Halobacteriota</t>
-  </si>
-  <si>
     <t>Archaeoglobi</t>
   </si>
   <si>
@@ -229,9 +235,6 @@
     <t>Syntropharchaeia</t>
   </si>
   <si>
-    <t>Methanobacteriota</t>
-  </si>
-  <si>
     <t>Methanobacteria</t>
   </si>
   <si>
@@ -241,21 +244,12 @@
     <t>Methanopyri</t>
   </si>
   <si>
-    <t>Methanobacteriota_B</t>
-  </si>
-  <si>
     <t>Thermococci</t>
   </si>
   <si>
-    <t>Nanohalarchaeota</t>
-  </si>
-  <si>
     <t>Nanosalinia</t>
   </si>
   <si>
-    <t>Thermoplasmatota</t>
-  </si>
-  <si>
     <t>E2</t>
   </si>
   <si>
@@ -265,30 +259,15 @@
     <t>Thermoplasmata</t>
   </si>
   <si>
-    <t>DPANN</t>
-  </si>
-  <si>
-    <t>Aenigmatarchaeota</t>
-  </si>
-  <si>
     <t>Aenigmatarchaeia</t>
   </si>
   <si>
-    <t>Iainarchaeota</t>
-  </si>
-  <si>
     <t>Iainarchaeia</t>
   </si>
   <si>
-    <t>Micrarchaeota</t>
-  </si>
-  <si>
     <t>Micrarchaeia</t>
   </si>
   <si>
-    <t>Nanobdellota</t>
-  </si>
-  <si>
     <t>Nanobdellia</t>
   </si>
   <si>
@@ -1261,59 +1240,99 @@
     <t>Marchantiales</t>
   </si>
   <si>
-    <t>Description:</t>
-  </si>
-  <si>
-    <t>The file includes the following sheets:</t>
-  </si>
-  <si>
-    <t>Archaea_Phylum</t>
-  </si>
-  <si>
-    <t>Archaea_Class</t>
-  </si>
-  <si>
-    <t>Archaea_Order</t>
-  </si>
-  <si>
-    <t>Bacteria_Phylum</t>
-  </si>
-  <si>
-    <t>Bacteria_Class</t>
-  </si>
-  <si>
-    <t>Bacteria_Order</t>
-  </si>
-  <si>
-    <t>Eukaryota_Phylum</t>
-  </si>
-  <si>
-    <t>Eukaryota_Class</t>
-  </si>
-  <si>
-    <t>Eukaryota_Order</t>
-  </si>
-  <si>
-    <t>Supplementary Table 20 | Final taxonomic counts of retained genomes in GS-Liu2021-B at the phylum, class and order levels.</t>
-  </si>
-  <si>
-    <t>This Excel file contains the final taxonomic counts of genomes retained in the GS-Liu2021-B dataset after hierarchical taxonomic balancing.</t>
-  </si>
-  <si>
-    <t>Each sheet lists the corresponding taxa and the number of genomes retained (N_genomes) at the indicated taxonomic rank for GS-Liu2021-B.</t>
+    <t>Bigyra</t>
+  </si>
+  <si>
+    <t>Choanoflagellata</t>
+  </si>
+  <si>
+    <t>Dinophyceae</t>
+  </si>
+  <si>
+    <t>Eustigmatophyceae</t>
+  </si>
+  <si>
+    <t>Filasterea</t>
+  </si>
+  <si>
+    <t>Ichthyosporea</t>
+  </si>
+  <si>
+    <t>Pelagophyceae</t>
+  </si>
+  <si>
+    <t>Phaeophyceae</t>
+  </si>
+  <si>
+    <t>Longamoebia</t>
+  </si>
+  <si>
+    <t>Mastigamoebida</t>
+  </si>
+  <si>
+    <t>Diplomonadida</t>
+  </si>
+  <si>
+    <t>Isochrysidales</t>
+  </si>
+  <si>
+    <t>Peronosporales</t>
+  </si>
+  <si>
+    <t>Trichomonadida</t>
+  </si>
+  <si>
+    <t>Perkinsida</t>
+  </si>
+  <si>
+    <t>Oxymonadida</t>
+  </si>
+  <si>
+    <t>Bicosoecida</t>
+  </si>
+  <si>
+    <t>Opalinata</t>
+  </si>
+  <si>
+    <t>Thraustochytrida</t>
+  </si>
+  <si>
+    <t>Craspedida</t>
+  </si>
+  <si>
+    <t>Suessiales</t>
+  </si>
+  <si>
+    <t>Eustigmatales</t>
+  </si>
+  <si>
+    <t>Ichthyophonida</t>
+  </si>
+  <si>
+    <t>Pelagomonadales</t>
+  </si>
+  <si>
+    <t>Ectocarpales</t>
+  </si>
+  <si>
+    <t>Apusomonadida</t>
+  </si>
+  <si>
+    <t>Rotosphaerida</t>
+  </si>
+  <si>
+    <t>Rhodocyclales</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1325,6 +1344,17 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1349,10 +1379,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1371,7 +1403,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1413,108 +1445,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1522,80 +1460,31 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1625,22 +1514,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1655,38 +1544,13 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D7A4BE0-AFC2-E446-BBD3-6AA2C9F54C90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1695,72 +1559,72 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>410</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>422</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>411</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>412</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>413</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>414</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>415</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>416</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>417</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>418</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>419</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>420</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>423</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1769,40 +1633,40 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11" style="2" customWidth="1"/>
     <col min="5" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -1810,13 +1674,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -1824,13 +1688,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1838,13 +1702,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1852,13 +1716,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -1866,13 +1730,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
@@ -1880,13 +1744,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -1894,13 +1758,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -1908,13 +1772,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -1922,13 +1786,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -1936,13 +1800,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -1950,13 +1814,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
@@ -1964,13 +1828,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -1978,13 +1842,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -1992,13 +1856,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
@@ -2006,13 +1870,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
@@ -2020,13 +1884,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
@@ -2034,13 +1898,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -2048,13 +1912,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -2062,13 +1926,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
@@ -2076,13 +1940,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
@@ -2090,13 +1954,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -2104,13 +1968,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
@@ -2118,13 +1982,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -2132,13 +1996,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -2146,13 +2010,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="D27" s="2">
         <v>2</v>
@@ -2160,13 +2024,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
@@ -2174,13 +2038,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
@@ -2188,24 +2052,27 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="D30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D31" s="2">
         <v>2</v>
@@ -2213,13 +2080,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D32" s="2">
         <v>1</v>
@@ -2227,13 +2094,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
@@ -2241,13 +2108,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
@@ -2255,13 +2122,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
@@ -2269,13 +2136,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="D36" s="2">
         <v>1</v>
@@ -2283,13 +2150,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D37" s="2">
         <v>1</v>
@@ -2297,13 +2164,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D38" s="2">
         <v>1</v>
@@ -2311,13 +2178,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D39" s="2">
         <v>1</v>
@@ -2325,13 +2192,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="D40" s="2">
         <v>1</v>
@@ -2339,13 +2206,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="D41" s="2">
         <v>1</v>
@@ -2353,13 +2220,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D42" s="2">
         <v>1</v>
@@ -2367,13 +2234,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="D43" s="2">
         <v>1</v>
@@ -2381,13 +2248,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D44" s="2">
         <v>1</v>
@@ -2395,13 +2262,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D45" s="2">
         <v>1</v>
@@ -2409,13 +2276,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D46" s="2">
         <v>1</v>
@@ -2423,13 +2290,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D47" s="2">
         <v>1</v>
@@ -2437,13 +2304,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D48" s="2">
         <v>1</v>
@@ -2451,13 +2318,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D49" s="2">
         <v>2</v>
@@ -2465,13 +2332,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="D50" s="2">
         <v>1</v>
@@ -2479,13 +2346,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="D51" s="2">
         <v>1</v>
@@ -2493,26 +2360,375 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D52" s="2">
         <v>2</v>
       </c>
     </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D56" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D58" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D59" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D61" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D62" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D63" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D64" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D65" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D66" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D67" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D68" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D69" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D70" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D71" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D72" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D73" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D74" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D76" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D77" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2534,10 +2750,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2">
         <v>194</v>
@@ -2545,10 +2761,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="2">
         <v>23</v>
@@ -2556,10 +2772,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2">
         <v>157</v>
@@ -2567,10 +2783,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2">
         <v>4</v>
@@ -2578,10 +2794,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -2589,10 +2805,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2">
         <v>101</v>
@@ -2600,10 +2816,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2">
         <v>27</v>
@@ -2611,10 +2827,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2">
         <v>11</v>
@@ -2622,10 +2838,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
@@ -2633,10 +2849,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2">
         <v>26</v>
@@ -2644,10 +2860,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
@@ -2655,10 +2871,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2">
         <v>5</v>
@@ -2666,10 +2882,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2">
         <v>8</v>
@@ -2677,59 +2893,55 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C4">
-    <sortCondition ref="A2:A4"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11" style="2" customWidth="1"/>
     <col min="5" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2">
         <v>2</v>
@@ -2737,13 +2949,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2">
         <v>3</v>
@@ -2751,13 +2963,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -2765,13 +2977,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2">
         <v>40</v>
@@ -2779,13 +2991,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D6" s="2">
         <v>16</v>
@@ -2793,13 +3005,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2">
         <v>11</v>
@@ -2807,13 +3019,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2">
         <v>49</v>
@@ -2821,13 +3033,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2">
         <v>15</v>
@@ -2835,13 +3047,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -2849,13 +3061,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2">
         <v>3</v>
@@ -2863,13 +3075,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2">
         <v>48</v>
@@ -2877,13 +3089,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
@@ -2891,13 +3103,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D14" s="2">
         <v>4</v>
@@ -2905,13 +3117,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D15" s="2">
         <v>19</v>
@@ -2919,13 +3131,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2">
         <v>21</v>
@@ -2933,13 +3145,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
@@ -2947,13 +3159,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D18" s="2">
         <v>21</v>
@@ -2961,13 +3173,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D19" s="2">
         <v>21</v>
@@ -2975,13 +3187,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D20" s="2">
         <v>21</v>
@@ -2989,13 +3201,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2">
         <v>21</v>
@@ -3003,13 +3215,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -3017,13 +3229,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D23" s="2">
         <v>21</v>
@@ -3031,13 +3243,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D24" s="2">
         <v>28</v>
@@ -3045,13 +3257,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D25" s="2">
         <v>4</v>
@@ -3059,13 +3271,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -3073,13 +3285,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D27" s="2">
         <v>7</v>
@@ -3087,13 +3299,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D28" s="2">
         <v>58</v>
@@ -3101,13 +3313,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -3115,13 +3327,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D30" s="2">
         <v>14</v>
@@ -3129,13 +3341,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D31" s="2">
         <v>2</v>
@@ -3143,13 +3355,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D32" s="2">
         <v>16</v>
@@ -3157,13 +3369,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
@@ -3171,13 +3383,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" s="2">
         <v>17</v>
@@ -3185,13 +3397,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" s="2">
         <v>9</v>
@@ -3199,13 +3411,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D36" s="2">
         <v>1</v>
@@ -3213,10 +3425,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>71</v>
@@ -3227,13 +3439,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="D38" s="2">
         <v>2</v>
@@ -3241,13 +3453,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D39" s="2">
         <v>1</v>
@@ -3255,13 +3467,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D40" s="2">
         <v>5</v>
@@ -3269,13 +3481,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D41" s="2">
         <v>20</v>
@@ -3283,13 +3495,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D42" s="2">
         <v>2</v>
@@ -3297,13 +3509,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D43" s="2">
         <v>5</v>
@@ -3311,13 +3523,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D44" s="2">
         <v>8</v>
@@ -3325,13 +3537,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D45" s="2">
         <v>9</v>
@@ -3339,51 +3551,50 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" style="2" customWidth="1"/>
     <col min="5" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2">
         <v>2</v>
@@ -3391,16 +3602,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2">
         <v>3</v>
@@ -3408,16 +3619,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2">
         <v>2</v>
@@ -3425,16 +3636,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E5" s="2">
         <v>12</v>
@@ -3442,16 +3653,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2">
         <v>17</v>
@@ -3459,16 +3670,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E7" s="2">
         <v>11</v>
@@ -3476,16 +3687,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E8" s="2">
         <v>16</v>
@@ -3493,16 +3704,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E9" s="2">
         <v>11</v>
@@ -3510,16 +3721,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
@@ -3527,16 +3738,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2">
         <v>44</v>
@@ -3544,16 +3755,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E12" s="2">
         <v>15</v>
@@ -3561,16 +3772,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E13" s="2">
         <v>2</v>
@@ -3578,16 +3789,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E14" s="2">
         <v>3</v>
@@ -3595,16 +3806,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2">
         <v>48</v>
@@ -3612,16 +3823,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E16" s="2">
         <v>3</v>
@@ -3629,16 +3840,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2">
         <v>3</v>
@@ -3646,16 +3857,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -3663,16 +3874,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E19" s="2">
         <v>2</v>
@@ -3680,16 +3891,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E20" s="2">
         <v>17</v>
@@ -3697,16 +3908,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E21" s="2">
         <v>2</v>
@@ -3714,16 +3925,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E22" s="2">
         <v>3</v>
@@ -3731,16 +3942,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E23" s="2">
         <v>6</v>
@@ -3748,16 +3959,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E24" s="2">
         <v>2</v>
@@ -3765,16 +3976,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E25" s="2">
         <v>2</v>
@@ -3782,16 +3993,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E26" s="2">
         <v>2</v>
@@ -3799,16 +4010,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E27" s="2">
         <v>2</v>
@@ -3816,16 +4027,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E28" s="2">
         <v>2</v>
@@ -3833,16 +4044,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2">
         <v>1</v>
@@ -3850,16 +4061,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E30" s="2">
         <v>21</v>
@@ -3867,16 +4078,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E31" s="2">
         <v>2</v>
@@ -3884,16 +4095,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E32" s="2">
         <v>6</v>
@@ -3901,16 +4112,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E33" s="2">
         <v>7</v>
@@ -3918,16 +4129,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E34" s="2">
         <v>6</v>
@@ -3935,16 +4146,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
@@ -3952,16 +4163,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E36" s="2">
         <v>20</v>
@@ -3969,16 +4180,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E37" s="2">
         <v>21</v>
@@ -3986,16 +4197,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E38" s="2">
         <v>1</v>
@@ -4003,16 +4214,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E39" s="2">
         <v>1</v>
@@ -4020,16 +4231,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E40" s="2">
         <v>6</v>
@@ -4037,16 +4248,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E41" s="2">
         <v>15</v>
@@ -4054,16 +4265,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E42" s="2">
         <v>28</v>
@@ -4071,16 +4282,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E43" s="2">
         <v>2</v>
@@ -4088,16 +4299,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E44" s="2">
         <v>2</v>
@@ -4105,16 +4316,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E45" s="2">
         <v>1</v>
@@ -4122,16 +4333,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E46" s="2">
         <v>7</v>
@@ -4139,16 +4350,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E47" s="2">
         <v>58</v>
@@ -4156,16 +4367,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E48" s="2">
         <v>3</v>
@@ -4173,16 +4384,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
@@ -4190,16 +4401,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E50" s="2">
         <v>2</v>
@@ -4207,16 +4418,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E51" s="2">
         <v>12</v>
@@ -4224,16 +4435,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E52" s="2">
         <v>1</v>
@@ -4241,16 +4452,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E53" s="2">
         <v>3</v>
@@ -4258,16 +4469,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E54" s="2">
         <v>1</v>
@@ -4275,16 +4486,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E55" s="2">
         <v>17</v>
@@ -4292,16 +4503,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E56" s="2">
         <v>9</v>
@@ -4309,16 +4520,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E57" s="2">
         <v>1</v>
@@ -4326,16 +4537,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E58" s="2">
         <v>1</v>
@@ -4343,16 +4554,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E59" s="2">
         <v>10</v>
@@ -4360,16 +4571,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E60" s="2">
         <v>2</v>
@@ -4377,16 +4588,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E61" s="2">
         <v>1</v>
@@ -4394,16 +4605,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="D62" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E62" s="2">
         <v>1</v>
@@ -4411,16 +4622,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="D63" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E63" s="2">
         <v>4</v>
@@ -4428,16 +4639,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E64" s="2">
         <v>2</v>
@@ -4445,16 +4656,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E65" s="2">
         <v>6</v>
@@ -4462,16 +4673,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E66" s="2">
         <v>1</v>
@@ -4479,16 +4690,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E67" s="2">
         <v>10</v>
@@ -4496,16 +4707,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E68" s="2">
         <v>1</v>
@@ -4513,16 +4724,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E69" s="2">
         <v>1</v>
@@ -4530,16 +4741,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E70" s="2">
         <v>1</v>
@@ -4547,16 +4758,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E71" s="2">
         <v>1</v>
@@ -4564,16 +4775,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E72" s="2">
         <v>4</v>
@@ -4581,16 +4792,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D73" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E73" s="2">
         <v>2</v>
@@ -4598,16 +4809,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D74" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E74" s="2">
         <v>2</v>
@@ -4615,16 +4826,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D75" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E75" s="2">
         <v>4</v>
@@ -4632,16 +4843,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E76" s="2">
         <v>1</v>
@@ -4649,16 +4860,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E77" s="2">
         <v>1</v>
@@ -4666,16 +4877,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E78" s="2">
         <v>7</v>
@@ -4683,31 +4894,30 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="2" customWidth="1"/>
     <col min="3" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B2" s="2">
         <v>18</v>
@@ -4715,7 +4925,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -4723,7 +4933,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B4" s="2">
         <v>14</v>
@@ -4731,7 +4941,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -4739,7 +4949,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -4747,7 +4957,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
@@ -4755,7 +4965,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
@@ -4763,7 +4973,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
@@ -4771,7 +4981,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -4779,7 +4989,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
@@ -4787,7 +4997,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -4795,7 +5005,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -4803,7 +5013,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -4811,7 +5021,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
@@ -4819,7 +5029,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
@@ -4827,7 +5037,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
@@ -4835,7 +5045,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -4843,7 +5053,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -4851,7 +5061,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -4859,15 +5069,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B21" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -4875,7 +5085,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -4883,7 +5093,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
@@ -4891,46 +5101,53 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B25" s="2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11" style="2" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -4938,10 +5155,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C3" s="2">
         <v>12</v>
@@ -4949,10 +5166,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C4" s="2">
         <v>4</v>
@@ -4960,10 +5177,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -4971,10 +5188,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
@@ -4982,10 +5199,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C7" s="2">
         <v>6</v>
@@ -4993,10 +5210,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C8" s="2">
         <v>3</v>
@@ -5004,10 +5221,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -5015,10 +5232,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
@@ -5026,10 +5243,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -5037,10 +5254,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -5048,10 +5265,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
@@ -5059,10 +5276,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C14" s="2">
         <v>5</v>
@@ -5070,10 +5287,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -5081,10 +5298,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
@@ -5092,10 +5309,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
@@ -5103,10 +5320,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
@@ -5114,10 +5331,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -5125,10 +5342,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C20" s="2">
         <v>5</v>
@@ -5136,10 +5353,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -5147,10 +5364,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -5158,10 +5375,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -5169,10 +5386,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -5180,10 +5397,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -5191,10 +5408,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -5202,10 +5419,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -5213,10 +5430,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -5224,10 +5441,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2">
         <v>2</v>
@@ -5235,10 +5452,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C30" s="2">
         <v>10</v>
@@ -5246,21 +5463,21 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C32" s="2">
         <v>19</v>
@@ -5268,10 +5485,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -5279,10 +5496,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -5290,10 +5507,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -5301,10 +5518,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -5312,56 +5529,66 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D68"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="2" customWidth="1"/>
     <col min="5" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -5369,13 +5596,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D3" s="2">
         <v>7</v>
@@ -5383,13 +5610,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -5397,13 +5624,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -5411,13 +5638,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -5425,13 +5652,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D7" s="2">
         <v>4</v>
@@ -5439,13 +5666,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -5453,13 +5680,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -5467,13 +5694,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -5481,13 +5708,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -5495,13 +5722,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -5509,13 +5736,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
@@ -5523,13 +5750,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
@@ -5537,13 +5764,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -5551,13 +5778,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
@@ -5565,13 +5792,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -5579,13 +5806,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
@@ -5593,13 +5820,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -5607,13 +5834,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -5621,13 +5848,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
@@ -5635,13 +5862,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
@@ -5649,13 +5876,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -5663,13 +5890,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -5677,13 +5904,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
@@ -5691,13 +5918,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -5705,13 +5932,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -5719,13 +5946,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
@@ -5733,13 +5960,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
@@ -5747,13 +5974,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -5761,13 +5988,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -5775,13 +6002,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D32" s="2">
         <v>1</v>
@@ -5789,13 +6016,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
@@ -5803,13 +6030,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D34" s="2">
         <v>3</v>
@@ -5817,13 +6044,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
@@ -5831,13 +6058,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D36" s="2">
         <v>1</v>
@@ -5845,13 +6072,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D37" s="2">
         <v>1</v>
@@ -5859,13 +6086,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D38" s="2">
         <v>1</v>
@@ -5873,13 +6100,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D39" s="2">
         <v>1</v>
@@ -5887,13 +6114,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D40" s="2">
         <v>1</v>
@@ -5901,13 +6128,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D41" s="2">
         <v>1</v>
@@ -5915,13 +6142,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D42" s="2">
         <v>1</v>
@@ -5929,13 +6156,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D43" s="2">
         <v>1</v>
@@ -5943,13 +6170,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D44" s="2">
         <v>1</v>
@@ -5957,13 +6184,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D45" s="2">
         <v>1</v>
@@ -5971,13 +6198,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D46" s="2">
         <v>1</v>
@@ -5985,13 +6212,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D47" s="2">
         <v>1</v>
@@ -5999,13 +6226,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D48" s="2">
         <v>1</v>
@@ -6013,13 +6240,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D49" s="2">
         <v>1</v>
@@ -6027,13 +6254,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D50" s="2">
         <v>3</v>
@@ -6041,13 +6268,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D51" s="2">
         <v>2</v>
@@ -6055,13 +6282,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D52" s="2">
         <v>1</v>
@@ -6069,13 +6296,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D53" s="2">
         <v>1</v>
@@ -6083,27 +6310,27 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D54" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>273</v>
+        <v>430</v>
       </c>
       <c r="D55" s="2">
         <v>1</v>
@@ -6111,69 +6338,69 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D56" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="D57" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D58" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D59" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D60" s="2">
         <v>1</v>
@@ -6181,13 +6408,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D61" s="2">
         <v>1</v>
@@ -6195,13 +6422,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D62" s="2">
         <v>1</v>
@@ -6209,13 +6436,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="D63" s="2">
         <v>1</v>
@@ -6223,13 +6450,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D64" s="2">
         <v>1</v>
@@ -6237,13 +6464,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D65" s="2">
         <v>1</v>
@@ -6251,13 +6478,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D66" s="2">
         <v>1</v>
@@ -6265,13 +6492,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D67" s="2">
         <v>1</v>
@@ -6279,45 +6506,72 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D68" s="2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D69" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="2" customWidth="1"/>
     <col min="3" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -6325,7 +6579,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -6333,7 +6587,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
@@ -6341,7 +6595,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B5" s="2">
         <v>10</v>
@@ -6349,7 +6603,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
@@ -6357,7 +6611,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
@@ -6365,7 +6619,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
@@ -6373,7 +6627,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
@@ -6381,7 +6635,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
@@ -6389,7 +6643,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
@@ -6397,7 +6651,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B12" s="2">
         <v>1</v>
@@ -6405,7 +6659,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -6413,7 +6667,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -6421,7 +6675,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
@@ -6429,7 +6683,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
@@ -6437,7 +6691,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
@@ -6445,7 +6699,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -6453,7 +6707,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B19" s="2">
         <v>2</v>
@@ -6461,7 +6715,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
@@ -6469,7 +6723,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B21" s="2">
         <v>1</v>
@@ -6477,7 +6731,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B22" s="2">
         <v>1</v>
@@ -6485,7 +6739,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -6493,7 +6747,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
@@ -6501,7 +6755,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B25" s="2">
         <v>1</v>
@@ -6509,7 +6763,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B26" s="2">
         <v>2</v>
@@ -6517,7 +6771,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
@@ -6525,7 +6779,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
@@ -6533,7 +6787,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
@@ -6541,7 +6795,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B30" s="2">
         <v>1</v>
@@ -6549,7 +6803,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
@@ -6557,7 +6811,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B32" s="2">
         <v>1</v>
@@ -6565,7 +6819,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B33" s="2">
         <v>1</v>
@@ -6573,7 +6827,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B34" s="2">
         <v>1</v>
@@ -6581,7 +6835,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B35" s="2">
         <v>4</v>
@@ -6589,46 +6843,53 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B36" s="2">
         <v>15</v>
       </c>
     </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="2">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="2" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -6636,10 +6897,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -6647,10 +6908,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -6658,10 +6919,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -6669,10 +6930,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -6680,10 +6941,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C7" s="2">
         <v>2</v>
@@ -6691,10 +6952,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -6702,10 +6963,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C9" s="2">
         <v>2</v>
@@ -6713,10 +6974,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
@@ -6724,10 +6985,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -6735,10 +6996,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -6746,10 +7007,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
@@ -6757,10 +7018,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -6768,10 +7029,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -6779,10 +7040,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -6790,10 +7051,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -6801,10 +7062,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -6812,10 +7073,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -6823,10 +7084,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
@@ -6834,10 +7095,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -6845,10 +7106,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -6856,10 +7117,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -6867,10 +7128,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -6878,26 +7139,32 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C25" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -6905,10 +7172,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C28" s="2">
         <v>2</v>
@@ -6916,10 +7183,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -6927,18 +7194,21 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -6946,50 +7216,65 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>305</v>
+        <v>298</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>306</v>
+        <v>299</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>307</v>
+        <v>300</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -6997,10 +7282,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -7008,10 +7293,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -7019,34 +7304,43 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -7054,10 +7348,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -7065,10 +7359,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -7076,18 +7370,21 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2">
         <v>3</v>
@@ -7095,10 +7392,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -7106,10 +7403,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -7117,10 +7414,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -7128,10 +7425,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -7139,10 +7436,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C52" s="2">
         <v>10</v>
@@ -7150,17 +7447,115 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C53" s="2">
         <v>2</v>
       </c>
     </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C54" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C62" s="2">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>